--- a/human_resources_forms/006_payroll_statement_copy_request_form--human_resources_forms.xlsx
+++ b/human_resources_forms/006_payroll_statement_copy_request_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1325,8 +1325,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'accounting'}</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Accounting'}</t>
+          <t>Accounting</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'management'}</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Management'}</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'requesting_a_copy_for_my_records'}</t>
+          <t>requesting_a_copy_for_my_records</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Requesting a copy for my records'}</t>
+          <t>Requesting a copy for my records</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'requesting_for_my_manager'}</t>
+          <t>requesting_for_my_manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Requesting for my manager'}</t>
+          <t>Requesting for my manager</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'requesting_for_hr'}</t>
+          <t>requesting_for_hr</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Requesting for HR'}</t>
+          <t>Requesting for HR</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'submit_form'}</t>
+          <t>submit_form</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Submit Form'}</t>
+          <t>Submit Form</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'save_for_later'}</t>
+          <t>save_for_later</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Save for Later'}</t>
+          <t>Save for Later</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'accounting'}</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Accounting'}</t>
+          <t>Accounting</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'management'}</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Management'}</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
